--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513256_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513256_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9003</v>
+        <v>6.7615</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7046</v>
+        <v>7.3641</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8043</v>
+        <v>-0.6026</v>
       </c>
       <c r="G2" t="n">
         <v>3.9637</v>
@@ -610,13 +610,13 @@
         <v>1.3216</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4124</v>
+        <v>1.2736</v>
       </c>
       <c r="T2" t="n">
-        <v>1.27</v>
+        <v>0.9295</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1424</v>
+        <v>0.3441</v>
       </c>
       <c r="V2" t="n">
         <v>1.3039</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1769</v>
+        <v>5.2347</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3636</v>
+        <v>4.217</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8133</v>
+        <v>1.0177</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8345</v>
+        <v>0.1704</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4461</v>
+        <v>0.4285</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3884</v>
+        <v>-0.2581</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5369</v>
+        <v>1.5433</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1028</v>
+        <v>0.7728</v>
       </c>
       <c r="L3" t="n">
-        <v>0.434</v>
+        <v>0.7705</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7024</v>
+        <v>-1.3729</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6567</v>
+        <v>-0.3443</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0457</v>
+        <v>-1.0286</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8811</v>
+        <v>2.2027</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8811</v>
+        <v>2.2027</v>
       </c>
       <c r="S3" t="n">
-        <v>1.153</v>
+        <v>0.6237</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2922</v>
+        <v>0.4358</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4452</v>
+        <v>0.1879</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3084</v>
+        <v>2.2378</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1189</v>
+        <v>2.2378</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9041</v>
+        <v>5.08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9871</v>
+        <v>3.8432</v>
       </c>
       <c r="F4" t="n">
-        <v>0.917</v>
+        <v>1.2368</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0421</v>
+        <v>1.8345</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2061</v>
+        <v>1.4461</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1639</v>
+        <v>0.3884</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3478</v>
+        <v>2.5369</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5504</v>
+        <v>2.1028</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7974</v>
+        <v>0.434</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3056</v>
+        <v>-0.7024</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3443</v>
+        <v>-0.6567</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9613</v>
+        <v>-0.0457</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7622</v>
+        <v>0.8811</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7622</v>
+        <v>0.8811</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9148</v>
+        <v>1.0561</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8949</v>
+        <v>0.1874</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0199</v>
+        <v>0.8687</v>
       </c>
       <c r="V4" t="n">
-        <v>0.185</v>
+        <v>1.3084</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7444</v>
+        <v>1.1189</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5595</v>
+        <v>0.1895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0206</v>
+        <v>3.6383</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2047</v>
+        <v>3.1248</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8159</v>
+        <v>0.5135</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1704</v>
+        <v>0.0421</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4285</v>
+        <v>0.2061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2581</v>
+        <v>-0.1639</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5433</v>
+        <v>1.3478</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7728</v>
+        <v>0.5504</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7705</v>
+        <v>0.7974</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3729</v>
+        <v>-1.3056</v>
       </c>
       <c r="N5" t="n">
         <v>-0.3443</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0286</v>
+        <v>-0.9613</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2027</v>
+        <v>1.7622</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2027</v>
+        <v>1.7622</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5904</v>
+        <v>1.6489</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5765</v>
+        <v>1.0326</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0139</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>2.2378</v>
+        <v>0.185</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2378</v>
+        <v>0.7444</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5595</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0839</v>
+        <v>2.9668</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8522</v>
+        <v>2.7351</v>
       </c>
       <c r="F6" t="n">
         <v>0.2317</v>
@@ -922,10 +922,10 @@
         <v>0.8811</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0641</v>
+        <v>-0.0531</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1686</v>
+        <v>0.0515</v>
       </c>
       <c r="U6" t="n">
         <v>-0.1046</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. MICOVIC</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3361</v>
+        <v>1.5243</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0425</v>
+        <v>2.42</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2936</v>
+        <v>-0.8957000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7461</v>
+        <v>0.4481</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9686</v>
+        <v>2.7111</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2225</v>
+        <v>-2.263</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9112</v>
+        <v>0.0118</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7973</v>
+        <v>2.0946</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1139</v>
+        <v>-2.0827</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1651</v>
+        <v>0.4363</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1714</v>
+        <v>0.6165</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3365</v>
+        <v>-0.1803</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4405</v>
+        <v>0.4405</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3216</v>
+        <v>-0.2203</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8811</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0306</v>
+        <v>-0.1132</v>
       </c>
       <c r="T7" t="n">
-        <v>0.453</v>
+        <v>-0.1688</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4224</v>
+        <v>0.0556</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.7489</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.7973</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.0483</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>S. MICOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8846000000000001</v>
+        <v>1.5118</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0685</v>
+        <v>0.8723</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.184</v>
+        <v>0.6395</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4481</v>
+        <v>1.7461</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7111</v>
+        <v>1.9686</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.263</v>
+        <v>-0.2225</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0118</v>
+        <v>1.9112</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0946</v>
+        <v>1.7973</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0827</v>
+        <v>0.1139</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4363</v>
+        <v>-0.1651</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6165</v>
+        <v>0.1714</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1803</v>
+        <v>-0.3365</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4405</v>
+        <v>-0.4405</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2203</v>
+        <v>-1.3216</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.8811</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.753</v>
+        <v>0.2062</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5203</v>
+        <v>0.2827</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2327</v>
+        <v>-0.0765</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7489</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.7973</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.0483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4932</v>
+        <v>0.5508</v>
       </c>
       <c r="E9" t="n">
         <v>0.4409</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0522</v>
+        <v>0.1099</v>
       </c>
       <c r="G9" t="n">
         <v>0.5188</v>
@@ -1156,13 +1156,13 @@
         <v>0.2203</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2459</v>
+        <v>-0.1882</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1922</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0537</v>
+        <v>0.0039</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4816</v>
+        <v>0.1077</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7349</v>
+        <v>-1.0223</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2165</v>
+        <v>1.13</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3576</v>
@@ -1234,13 +1234,13 @@
         <v>1.3216</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1078</v>
+        <v>0.7339</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0138</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.094</v>
+        <v>0.0075</v>
       </c>
       <c r="V10" t="n">
         <v>-0.37</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9488</v>
+        <v>-1.0768</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7395</v>
+        <v>-2.5992</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7907999999999999</v>
+        <v>1.5223</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0908</v>
+        <v>0.9668</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6262</v>
+        <v>-0.3277</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4646</v>
+        <v>1.2944</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9257</v>
+        <v>2.1835</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7976</v>
+        <v>-0.2958</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1281</v>
+        <v>2.4793</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1651</v>
+        <v>-1.2167</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1714</v>
+        <v>-0.0319</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3365</v>
+        <v>-1.1848</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4405</v>
+        <v>-2.2027</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3216</v>
+        <v>-4.4054</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8811</v>
+        <v>2.2027</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4637</v>
+        <v>0.9081</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3889</v>
+        <v>0.3718</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.5363</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1189</v>
+        <v>-0.7489</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1189</v>
+        <v>-0.7489</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1756</v>
+        <v>-1.1812</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6115</v>
+        <v>-1.8567</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4358</v>
+        <v>0.6755</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9668</v>
+        <v>-2.0908</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3277</v>
+        <v>-0.6262</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2944</v>
+        <v>-1.4646</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1835</v>
+        <v>-1.9257</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2958</v>
+        <v>-0.7976</v>
       </c>
       <c r="L12" t="n">
-        <v>2.4793</v>
+        <v>-1.1281</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2167</v>
+        <v>-0.1651</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0319</v>
+        <v>0.1714</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1848</v>
+        <v>-0.3365</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2027</v>
+        <v>-0.4405</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.4054</v>
+        <v>-1.3216</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2027</v>
+        <v>0.8811</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1907</v>
+        <v>0.2312</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6405999999999999</v>
+        <v>0.2717</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4498</v>
+        <v>-0.0405</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7489</v>
+        <v>1.1189</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7489</v>
+        <v>1.1189</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>24.1569</v>
+        <v>25.1179</v>
       </c>
       <c r="E13" t="n">
-        <v>18.5782</v>
+        <v>19.5392</v>
       </c>
       <c r="F13" t="n">
-        <v>5.5785</v>
+        <v>5.5786</v>
       </c>
       <c r="G13" t="n">
-        <v>7.297200000000001</v>
+        <v>7.2972</v>
       </c>
       <c r="H13" t="n">
         <v>12.6569</v>
@@ -1447,10 +1447,10 @@
         <v>11.9593</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3483999999999994</v>
+        <v>0.3483999999999996</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.010300000000001</v>
+        <v>-5.0103</v>
       </c>
       <c r="N13" t="n">
         <v>0.6975</v>
@@ -1468,10 +1468,10 @@
         <v>13.2163</v>
       </c>
       <c r="S13" t="n">
-        <v>5.366400000000001</v>
+        <v>6.3272</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9674</v>
+        <v>3.9283</v>
       </c>
       <c r="U13" t="n">
         <v>2.3988</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8334</v>
+        <v>3.2556</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8672</v>
+        <v>5.5157</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0338</v>
+        <v>-2.2601</v>
       </c>
       <c r="G14" t="n">
         <v>2.2103</v>
@@ -1546,13 +1546,13 @@
         <v>1.7622</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0377</v>
+        <v>-0.6156</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2451</v>
+        <v>-0.1064</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2828</v>
+        <v>-0.5092</v>
       </c>
       <c r="V14" t="n">
         <v>0.5595</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2347</v>
+        <v>1.3435</v>
       </c>
       <c r="E15" t="n">
-        <v>0.717</v>
+        <v>0.5998</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5177</v>
+        <v>0.7436</v>
       </c>
       <c r="G15" t="n">
         <v>1.1615</v>
@@ -1624,13 +1624,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0424</v>
+        <v>0.1512</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3968</v>
+        <v>0.2796</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3544</v>
+        <v>-0.1284</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1895</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4218</v>
+        <v>-1.1875</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0244</v>
+        <v>1.2587</v>
       </c>
       <c r="F17" t="n">
         <v>-2.4462</v>
@@ -1780,10 +1780,10 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.753</v>
+        <v>-0.5187</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4484</v>
+        <v>-0.2141</v>
       </c>
       <c r="U17" t="n">
         <v>-0.3046</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2709</v>
+        <v>-1.7762</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9566</v>
+        <v>-1.3708</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3143</v>
+        <v>-0.4055</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7973</v>
@@ -1858,13 +1858,13 @@
         <v>0.8811</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9142</v>
+        <v>-0.4195</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1889</v>
+        <v>-0.6031</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2748</v>
+        <v>0.1837</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4066</v>
+        <v>-2.0077</v>
       </c>
       <c r="E19" t="n">
         <v>-1.4314</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9752</v>
+        <v>-0.5763</v>
       </c>
       <c r="G19" t="n">
         <v>0.5261</v>
@@ -1936,13 +1936,13 @@
         <v>1.1014</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8313</v>
+        <v>-0.4324</v>
       </c>
       <c r="T19" t="n">
         <v>-0.4719</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3594</v>
+        <v>0.0395</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5595</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6764</v>
+        <v>-2.8418</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0811</v>
+        <v>-0.8747</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5953</v>
+        <v>-1.9671</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7149</v>
+        <v>-1.2243</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8124</v>
+        <v>0.4811</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09760000000000001</v>
+        <v>-1.7054</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5876</v>
+        <v>0.9532</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6635</v>
+        <v>1.4738</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0759</v>
+        <v>-0.5206</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1273</v>
+        <v>-2.1775</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1489</v>
+        <v>-0.9927</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0216</v>
+        <v>-1.1848</v>
       </c>
       <c r="P20" t="n">
         <v>-0.8811</v>
@@ -2014,28 +2014,28 @@
         <v>0.4405</v>
       </c>
       <c r="S20" t="n">
-        <v>0.479</v>
+        <v>-0.3664</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2686</v>
+        <v>-0.5062</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2103</v>
+        <v>0.1399</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5595</v>
+        <v>-0.37</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5595</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1189</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1337</v>
+        <v>-3.3757</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.109</v>
+        <v>-1.5498</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0247</v>
+        <v>-1.8259</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2243</v>
+        <v>-1.7149</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4811</v>
+        <v>-1.8124</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7054</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9532</v>
+        <v>-0.5876</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4738</v>
+        <v>-0.6635</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5206</v>
+        <v>0.0759</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1775</v>
+        <v>-1.1273</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9927</v>
+        <v>-1.1489</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1848</v>
+        <v>0.0216</v>
       </c>
       <c r="P21" t="n">
         <v>-0.8811</v>
@@ -2092,22 +2092,22 @@
         <v>0.4405</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6583</v>
+        <v>-0.2203</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7406</v>
+        <v>-0.2</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0822</v>
+        <v>-0.0203</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.37</v>
+        <v>-0.5595</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5595</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.37</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9569</v>
+        <v>-3.6445</v>
       </c>
       <c r="E22" t="n">
         <v>-0.6521</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3048</v>
+        <v>-2.9923</v>
       </c>
       <c r="G22" t="n">
         <v>0.6574</v>
@@ -2170,13 +2170,13 @@
         <v>1.1014</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.5046</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0516</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7654</v>
+        <v>-0.453</v>
       </c>
       <c r="V22" t="n">
         <v>-3.3567</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2631</v>
+        <v>-5.5282</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0544</v>
+        <v>-2.4059</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2088</v>
+        <v>-3.1223</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7836</v>
@@ -2248,13 +2248,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0139</v>
+        <v>-0.2512</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1046</v>
+        <v>-0.2469</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0907</v>
+        <v>-0.0042</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0528</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.6998</v>
+        <v>-6.4367</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4056</v>
+        <v>-5.1713</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2942</v>
+        <v>-1.2654</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6909</v>
@@ -2326,13 +2326,13 @@
         <v>1.1014</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6697</v>
+        <v>-0.4066</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3843</v>
+        <v>-0.15</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2854</v>
+        <v>-0.2565</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1189</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-24.1568</v>
+        <v>-22.5949</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.5786</v>
+        <v>-5.578799999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.5782</v>
+        <v>-17.0161</v>
       </c>
       <c r="G25" t="n">
         <v>-7.297199999999999</v>
@@ -2404,13 +2404,13 @@
         <v>8.8109</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.3662</v>
+        <v>-3.8044</v>
       </c>
       <c r="T25" t="n">
         <v>-2.3987</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.9676</v>
+        <v>-1.4053</v>
       </c>
       <c r="V25" t="n">
         <v>-7.087899999999999</v>
